--- a/Result/profitability/3704.xlsx
+++ b/Result/profitability/3704.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.50125</v>
+        <v>0.69375</v>
       </c>
       <c r="N2" t="n">
-        <v>26.81875</v>
+        <v>26.94</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -8431,6 +8431,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8751</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6678</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2074</v>
+      </c>
+      <c r="F64" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G64" t="n">
+        <v>707</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>8.08%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>711</v>
+      </c>
+      <c r="K64" t="n">
+        <v>513</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="N64" t="n">
+        <v>25.535</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="X64" t="n">
+        <v>3.344827586206897</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-0.3100000000000023</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.0129112869637652</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-2.340425531914894</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-0.629999999999999</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-0.02589395807644879</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
